--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DAMEX CB ALGECIRAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DAMEX CB ALGECIRAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9203</v>
+        <v>21.4321</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7281</v>
+        <v>20.5365</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1922</v>
+        <v>0.8959000000000004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6966</v>
+        <v>3.2596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7442</v>
+        <v>3.9212</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0476</v>
+        <v>-0.6617000000000002</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4502</v>
+        <v>9.300699999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0102</v>
+        <v>7.2337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4399</v>
+        <v>2.0669</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7536</v>
+        <v>-6.041</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2661</v>
+        <v>-3.3125</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4876</v>
+        <v>-2.7285</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4001000000000001</v>
+        <v>0.7789999999999998</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-7.205299999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4007</v>
+        <v>7.9842</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8568</v>
+        <v>9.663</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.08</v>
+        <v>5.091</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9368</v>
+        <v>4.5721</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9669</v>
+        <v>7.7306</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3584</v>
+        <v>13.3501</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3915</v>
+        <v>-5.6195</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.98</v>
+        <v>14.0846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5154000000000001</v>
+        <v>5.9709</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4646</v>
+        <v>8.1137</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8179</v>
+        <v>11.2085</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3599000000000001</v>
+        <v>5.1253</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4581</v>
+        <v>6.083299999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>2.873</v>
+        <v>13.618</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8124</v>
+        <v>7.2183</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0606</v>
+        <v>6.399899999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0551</v>
+        <v>-2.4095</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4525</v>
+        <v>-2.0928</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6025999999999999</v>
+        <v>-0.3166000000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0009</v>
+        <v>-14.4106</v>
       </c>
       <c r="R3" t="n">
-        <v>4.0012</v>
+        <v>12.0736</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.2458</v>
+        <v>-7.3287</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.616</v>
+        <v>-4.6818</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6298999999999999</v>
+        <v>-2.6469</v>
       </c>
       <c r="V3" t="n">
-        <v>3.4075</v>
+        <v>12.5416</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2592</v>
+        <v>11.4454</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1483</v>
+        <v>1.0964</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5855</v>
+        <v>12.3925</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1039</v>
+        <v>14.4544</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5185000000000002</v>
+        <v>-2.061900000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4249</v>
+        <v>4.9718</v>
       </c>
       <c r="H4" t="n">
-        <v>5.454499999999999</v>
+        <v>-3.0708</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9703</v>
+        <v>8.0427</v>
       </c>
       <c r="J4" t="n">
-        <v>9.794699999999999</v>
+        <v>8.6341</v>
       </c>
       <c r="K4" t="n">
-        <v>6.0219</v>
+        <v>-1.3133</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7728</v>
+        <v>9.9476</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3698</v>
+        <v>-3.6624</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5674</v>
+        <v>-1.7575</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8024</v>
+        <v>-1.9047</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.201</v>
+        <v>6.0368</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.0023</v>
+        <v>-1.1684</v>
       </c>
       <c r="R4" t="n">
-        <v>4.8014</v>
+        <v>7.2052</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.845800000000001</v>
+        <v>-3.2458</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.0672</v>
+        <v>-0.286</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.7786</v>
+        <v>-2.9597</v>
       </c>
       <c r="V4" t="n">
-        <v>3.2073</v>
+        <v>4.6296</v>
       </c>
       <c r="W4" t="n">
-        <v>4.3786</v>
+        <v>7.2748</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1714</v>
+        <v>-2.6451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6427</v>
+        <v>7.398300000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.849</v>
+        <v>6.2589</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2063</v>
+        <v>1.1394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1504000000000001</v>
+        <v>5.9262</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3186</v>
+        <v>1.0451</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4689</v>
+        <v>4.881</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4674</v>
+        <v>10.3964</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.096</v>
+        <v>3.6104</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5634</v>
+        <v>6.786</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3169</v>
+        <v>-4.4702</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2226</v>
+        <v>-2.5654</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0945</v>
+        <v>-1.9049</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4007</v>
+        <v>-0.9737000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-11.1001</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4007</v>
+        <v>10.1263</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9881</v>
+        <v>4.4391</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0179</v>
+        <v>4.013</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9702000000000001</v>
+        <v>0.426</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0798</v>
+        <v>-1.9932</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3995</v>
+        <v>2.9496</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3197</v>
+        <v>-4.9428</v>
       </c>
     </row>
     <row r="6">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9273</v>
+        <v>2.0572</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4947</v>
+        <v>-1.0312</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4221</v>
+        <v>3.0885</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4503</v>
+        <v>2.1051</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9360999999999999</v>
+        <v>-0.6446000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5142</v>
+        <v>2.7498</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5815</v>
+        <v>1.3427</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7016</v>
+        <v>-1.3726</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8799</v>
+        <v>2.7154</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1310999999999999</v>
+        <v>0.7624000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2345</v>
+        <v>0.7278</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3657</v>
+        <v>0.03459999999999996</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4001</v>
+        <v>1.3631</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0009</v>
+        <v>-5.0632</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6007</v>
+        <v>6.426299999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2569</v>
+        <v>2.5505</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.07539999999999997</v>
+        <v>2.4098</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3323</v>
+        <v>0.1405999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3798</v>
+        <v>-3.9617</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3798</v>
+        <v>-4.2412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5506000000000002</v>
+        <v>0.7214999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.231</v>
+        <v>0.3832999999999998</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7817</v>
+        <v>0.3381999999999996</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7179000000000002</v>
+        <v>6.844399999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.513</v>
+        <v>6.0999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2049</v>
+        <v>0.7444000000000006</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7783</v>
+        <v>11.4998</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1109</v>
+        <v>7.323</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8892</v>
+        <v>4.1768</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4962</v>
+        <v>-4.6554</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.402</v>
+        <v>-1.223</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0942</v>
+        <v>-3.4324</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8002000000000001</v>
+        <v>-6.8157</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>-16.942</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8011</v>
+        <v>10.1263</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4264</v>
+        <v>-8.1295</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7341</v>
+        <v>-4.4501</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3078</v>
+        <v>-3.6795</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0595</v>
+        <v>8.8225</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7194</v>
+        <v>10.2759</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.7788</v>
+        <v>-1.4533</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. PANOS HUERTAS</t>
+          <t>K. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7469</v>
+        <v>0.4698</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2378</v>
+        <v>0.4698</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5091</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.173</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3086</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1356</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3286</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1356</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3741</v>
+        <v>0.6645</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2578</v>
+        <v>0.6645</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1163</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2036</v>
+        <v>0.4089000000000003</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1352</v>
+        <v>3.9359</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9315</v>
+        <v>-3.5272</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7774</v>
+        <v>5.470699999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6349</v>
+        <v>-0.7441999999999998</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8574000000000001</v>
+        <v>6.2149</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4027</v>
+        <v>8.078900000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.612</v>
+        <v>1.3014</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2093</v>
+        <v>6.7775</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3748</v>
+        <v>-2.6082</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02290000000000003</v>
+        <v>-2.0455</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3519</v>
+        <v>-0.5627</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0003</v>
+        <v>-6.2317</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0006</v>
+        <v>-14.8</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0009</v>
+        <v>8.5684</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.1741</v>
+        <v>0.2873999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7914</v>
+        <v>1.2497</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3827</v>
+        <v>-0.9623</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7477</v>
+        <v>0.8823999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>2.0594</v>
+        <v>9.407500000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3117</v>
+        <v>-8.5251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>A. MONTENEGRO MOYA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0934</v>
+        <v>-0.2043000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.864</v>
+        <v>-0.3184</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2294</v>
+        <v>0.114</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6151</v>
+        <v>-0.1395</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3419</v>
+        <v>0.1329</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7267</v>
+        <v>-0.2724</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6611</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6687</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0076</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0459</v>
+        <v>-0.1395</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6732</v>
+        <v>0.1329</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7191</v>
+        <v>-0.2724</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.8011</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.0017</v>
+        <v>-0.1947</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2006</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.304</v>
+        <v>0.1298</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1207</v>
+        <v>-0.1237</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1833</v>
+        <v>0.2535</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01890000000000003</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6782</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>L. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,148 +1264,304 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.709300000000001</v>
+        <v>-2.7885</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4013</v>
+        <v>-1.0329</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3081</v>
+        <v>-1.7557</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1186</v>
+        <v>0.8672000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8653000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.236</v>
+        <v>1.7325</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0864</v>
+        <v>-0.3094</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1381</v>
+        <v>-1.8088</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9483</v>
+        <v>1.4995</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03220000000000001</v>
+        <v>1.1765</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7445000000000001</v>
+        <v>0.9435</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7122999999999999</v>
+        <v>0.2329999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>-0.1947</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8005</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2189</v>
+        <v>-2.1356</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6932</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4744</v>
+        <v>-1.6069</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1715</v>
+        <v>-2.8834</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3793</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5507</v>
+        <v>-2.8834</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>E. EGEA SOLER</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DAMEX CB ALGECIRAS</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-8.388200000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-7.583299999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.805</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-5.976</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-7.0642</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.0883</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.9531</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-3.4711</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.5182</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-4.0228</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-3.593</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.4298</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-7.2053</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8.179</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-7.7217</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-4.1993</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-3.5225</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.3357</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.7744</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.4387</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A. DIAZ ROLLANO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DAMEX CB ALGECIRAS</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-11.1963</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-8.998799999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.1976</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-6.1227</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.2632</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-4.8595</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-3.4709</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-3.9047</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-2.6518</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1.697</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.9549000000000001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-2.5316</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-8.178900000000001</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.6474</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.7206</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.6292999999999999</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-3.2625</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.2806</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-6.5431</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>DAMEX CB ALGECIRAS</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.248000000000002</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-1.7056</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.4572999999999997</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.138100000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-1.504900000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.6427</v>
-      </c>
-      <c r="J12" t="n">
-        <v>14.81489999999999</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.940399999999999</v>
-      </c>
-      <c r="L12" t="n">
-        <v>10.8744</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-9.6768</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-5.4453</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-4.2319</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-3.000899999999999</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-30.0088</v>
-      </c>
-      <c r="R12" t="n">
-        <v>27.0078</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-10.0027</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-7.7441</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-2.2587</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.617500000000001</v>
-      </c>
-      <c r="W12" t="n">
-        <v>21.232</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-14.6145</v>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>36.3876</v>
+      </c>
+      <c r="E14" t="n">
+        <v>33.04510000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.3423</v>
+      </c>
+      <c r="G14" t="n">
+        <v>28.4153</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.672099999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25.7433</v>
+      </c>
+      <c r="J14" t="n">
+        <v>57.13720000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19.1548</v>
+      </c>
+      <c r="L14" t="n">
+        <v>37.98309999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-28.72190000000001</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-16.4825</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-12.2393</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-8.763199999999998</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-86.65789999999998</v>
+      </c>
+      <c r="R14" t="n">
+        <v>77.89460000000001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-10.1064</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.470899999999999</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-8.635600000000002</v>
+      </c>
+      <c r="V14" t="n">
+        <v>26.8416</v>
+      </c>
+      <c r="W14" t="n">
+        <v>64.0378</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-37.1958</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DAMEX CB ALGECIRAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_DAMEX CB ALGECIRAS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>21.4321</v>
+        <v>19.1347</v>
       </c>
       <c r="E2" t="n">
-        <v>20.5365</v>
+        <v>9.308299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8959000000000004</v>
+        <v>9.826499999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2596</v>
+        <v>11.2085</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9212</v>
+        <v>5.1253</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6617000000000002</v>
+        <v>6.083299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>9.300699999999999</v>
+        <v>13.618</v>
       </c>
       <c r="K2" t="n">
-        <v>7.2337</v>
+        <v>7.2183</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0669</v>
+        <v>6.399899999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.041</v>
+        <v>-2.4095</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.3125</v>
+        <v>-2.0928</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.7285</v>
+        <v>-0.3166000000000002</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7789999999999998</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.205299999999999</v>
+        <v>-14.4106</v>
       </c>
       <c r="R2" t="n">
-        <v>7.9842</v>
+        <v>12.0736</v>
       </c>
       <c r="S2" t="n">
-        <v>9.663</v>
+        <v>-2.2786</v>
       </c>
       <c r="T2" t="n">
-        <v>5.091</v>
+        <v>-1.3445</v>
       </c>
       <c r="U2" t="n">
-        <v>4.5721</v>
+        <v>-0.9340999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>7.7306</v>
+        <v>12.5416</v>
       </c>
       <c r="W2" t="n">
-        <v>13.3501</v>
+        <v>11.4454</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.6195</v>
+        <v>1.0964</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>14.0846</v>
+        <v>14.403</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9709</v>
+        <v>16.2467</v>
       </c>
       <c r="F3" t="n">
-        <v>8.1137</v>
+        <v>-1.8437</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2085</v>
+        <v>3.2596</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1253</v>
+        <v>3.9212</v>
       </c>
       <c r="I3" t="n">
-        <v>6.083299999999999</v>
+        <v>-0.6617000000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>13.618</v>
+        <v>9.300699999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>7.2183</v>
+        <v>7.2337</v>
       </c>
       <c r="L3" t="n">
-        <v>6.399899999999999</v>
+        <v>2.0669</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4095</v>
+        <v>-6.041</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0928</v>
+        <v>-3.3125</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3166000000000002</v>
+        <v>-2.7285</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.3368</v>
+        <v>0.7789999999999998</v>
       </c>
       <c r="Q3" t="n">
-        <v>-14.4106</v>
+        <v>-7.205299999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0736</v>
+        <v>7.9842</v>
       </c>
       <c r="S3" t="n">
-        <v>-7.3287</v>
+        <v>2.634</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.6818</v>
+        <v>0.8013</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.6469</v>
+        <v>1.8328</v>
       </c>
       <c r="V3" t="n">
-        <v>12.5416</v>
+        <v>7.7306</v>
       </c>
       <c r="W3" t="n">
-        <v>11.4454</v>
+        <v>13.3501</v>
       </c>
       <c r="X3" t="n">
-        <v>1.0964</v>
+        <v>-5.6195</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>12.3925</v>
+        <v>14.393</v>
       </c>
       <c r="E4" t="n">
-        <v>14.4544</v>
+        <v>14.8873</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.061900000000001</v>
+        <v>-0.4944</v>
       </c>
       <c r="G4" t="n">
         <v>4.9718</v>
@@ -766,13 +766,13 @@
         <v>7.2052</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.2458</v>
+        <v>-1.2455</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.286</v>
+        <v>0.1468999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.9597</v>
+        <v>-1.3923</v>
       </c>
       <c r="V4" t="n">
         <v>4.6296</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>7.398300000000001</v>
+        <v>5.8583</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2589</v>
+        <v>3.4456</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1394</v>
+        <v>2.4127</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9262</v>
+        <v>6.844399999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0451</v>
+        <v>6.0999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.881</v>
+        <v>0.7444000000000006</v>
       </c>
       <c r="J5" t="n">
-        <v>10.3964</v>
+        <v>11.4998</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6104</v>
+        <v>7.323</v>
       </c>
       <c r="L5" t="n">
-        <v>6.786</v>
+        <v>4.1768</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.4702</v>
+        <v>-4.6554</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.5654</v>
+        <v>-1.223</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9049</v>
+        <v>-3.4324</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9737000000000001</v>
+        <v>-6.8157</v>
       </c>
       <c r="Q5" t="n">
-        <v>-11.1001</v>
+        <v>-16.942</v>
       </c>
       <c r="R5" t="n">
         <v>10.1263</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4391</v>
+        <v>-2.9929</v>
       </c>
       <c r="T5" t="n">
-        <v>4.013</v>
+        <v>-1.388</v>
       </c>
       <c r="U5" t="n">
-        <v>0.426</v>
+        <v>-1.6048</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9932</v>
+        <v>8.8225</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9496</v>
+        <v>10.2759</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.9428</v>
+        <v>-1.4533</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0572</v>
+        <v>3.8831</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0312</v>
+        <v>3.9247</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0885</v>
+        <v>-0.04169999999999963</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1051</v>
+        <v>5.9262</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6446000000000001</v>
+        <v>1.0451</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7498</v>
+        <v>4.881</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3427</v>
+        <v>10.3964</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3726</v>
+        <v>3.6104</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7154</v>
+        <v>6.786</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7624000000000002</v>
+        <v>-4.4702</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7278</v>
+        <v>-2.5654</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03459999999999996</v>
+        <v>-1.9049</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3631</v>
+        <v>-0.9737000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.0632</v>
+        <v>-11.1001</v>
       </c>
       <c r="R6" t="n">
-        <v>6.426299999999999</v>
+        <v>10.1263</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5505</v>
+        <v>0.9238</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4098</v>
+        <v>1.6788</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1405999999999999</v>
+        <v>-0.7551999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.9617</v>
+        <v>-1.9932</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2795</v>
+        <v>2.9496</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.2412</v>
+        <v>-4.9428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7214999999999999</v>
+        <v>1.6864</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3832999999999998</v>
+        <v>4.5305</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3381999999999996</v>
+        <v>-2.844</v>
       </c>
       <c r="G7" t="n">
-        <v>6.844399999999999</v>
+        <v>5.470699999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>6.0999</v>
+        <v>-0.7441999999999998</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7444000000000006</v>
+        <v>6.2149</v>
       </c>
       <c r="J7" t="n">
-        <v>11.4998</v>
+        <v>8.078900000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>7.323</v>
+        <v>1.3014</v>
       </c>
       <c r="L7" t="n">
-        <v>4.1768</v>
+        <v>6.7775</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.6554</v>
+        <v>-2.6082</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.223</v>
+        <v>-2.0455</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.4324</v>
+        <v>-0.5627</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.8157</v>
+        <v>-6.2317</v>
       </c>
       <c r="Q7" t="n">
-        <v>-16.942</v>
+        <v>-14.8</v>
       </c>
       <c r="R7" t="n">
-        <v>10.1263</v>
+        <v>8.5684</v>
       </c>
       <c r="S7" t="n">
-        <v>-8.1295</v>
+        <v>1.565</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.4501</v>
+        <v>1.844</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.6795</v>
+        <v>-0.279</v>
       </c>
       <c r="V7" t="n">
-        <v>8.8225</v>
+        <v>0.8823999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>10.2759</v>
+        <v>9.407500000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4533</v>
+        <v>-8.5251</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4698</v>
+        <v>0.0711</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4698</v>
+        <v>0.0711</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1078,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6645</v>
+        <v>0.2658</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6645</v>
+        <v>0.2658</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4089000000000003</v>
+        <v>0.02630000000000043</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9359</v>
+        <v>-2.1037</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5272</v>
+        <v>2.1298</v>
       </c>
       <c r="G9" t="n">
-        <v>5.470699999999999</v>
+        <v>2.1051</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7441999999999998</v>
+        <v>-0.6446000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2149</v>
+        <v>2.7498</v>
       </c>
       <c r="J9" t="n">
-        <v>8.078900000000001</v>
+        <v>1.3427</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3014</v>
+        <v>-1.3726</v>
       </c>
       <c r="L9" t="n">
-        <v>6.7775</v>
+        <v>2.7154</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6082</v>
+        <v>0.7624000000000002</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0455</v>
+        <v>0.7278</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5627</v>
+        <v>0.03459999999999996</v>
       </c>
       <c r="P9" t="n">
-        <v>-6.2317</v>
+        <v>1.3631</v>
       </c>
       <c r="Q9" t="n">
-        <v>-14.8</v>
+        <v>-5.0632</v>
       </c>
       <c r="R9" t="n">
-        <v>8.5684</v>
+        <v>6.426299999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2873999999999999</v>
+        <v>0.5196</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2497</v>
+        <v>1.3374</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9623</v>
+        <v>-0.8178000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8823999999999999</v>
+        <v>-3.9617</v>
       </c>
       <c r="W9" t="n">
-        <v>9.407500000000001</v>
+        <v>0.2795</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.5251</v>
+        <v>-4.2412</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2043000000000001</v>
+        <v>-0.1882</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3184</v>
+        <v>-0.2188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.114</v>
+        <v>0.03050000000000003</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1395</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1298</v>
+        <v>0.146</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1237</v>
+        <v>-0.02400000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2535</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7885</v>
+        <v>-1.8296</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0329</v>
+        <v>-0.07399999999999995</v>
       </c>
       <c r="F11" t="n">
         <v>-1.7557</v>
@@ -1312,13 +1312,13 @@
         <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1356</v>
+        <v>-1.1767</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5286999999999999</v>
+        <v>0.4301</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6069</v>
+        <v>-1.6068</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8834</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.388200000000001</v>
+        <v>-3.3351</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.583299999999999</v>
+        <v>-4.4592</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.805</v>
+        <v>1.124</v>
       </c>
       <c r="G12" t="n">
         <v>-5.976</v>
@@ -1390,13 +1390,13 @@
         <v>8.179</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.7217</v>
+        <v>-2.6684</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1993</v>
+        <v>-1.0751</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.5225</v>
+        <v>-1.5932</v>
       </c>
       <c r="V12" t="n">
         <v>4.3357</v>
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.1963</v>
+        <v>-11.6562</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.998799999999999</v>
+        <v>-9.1122</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1976</v>
+        <v>-2.544</v>
       </c>
       <c r="G13" t="n">
         <v>-6.1227</v>
@@ -1468,13 +1468,13 @@
         <v>5.6474</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7206</v>
+        <v>0.2607</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6292999999999999</v>
+        <v>-0.7430000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.0036</v>
       </c>
       <c r="V13" t="n">
         <v>-3.2625</v>
@@ -1501,16 +1501,16 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>36.3876</v>
+        <v>42.4468</v>
       </c>
       <c r="E14" t="n">
-        <v>33.04510000000001</v>
+        <v>36.4463</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3423</v>
+        <v>5.999999999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>28.4153</v>
+        <v>28.41529999999999</v>
       </c>
       <c r="H14" t="n">
         <v>2.672099999999999</v>
@@ -1519,13 +1519,13 @@
         <v>25.7433</v>
       </c>
       <c r="J14" t="n">
-        <v>57.13720000000001</v>
+        <v>57.1372</v>
       </c>
       <c r="K14" t="n">
         <v>19.1548</v>
       </c>
       <c r="L14" t="n">
-        <v>37.98309999999999</v>
+        <v>37.9831</v>
       </c>
       <c r="M14" t="n">
         <v>-28.72190000000001</v>
@@ -1546,13 +1546,13 @@
         <v>77.89460000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.1064</v>
+        <v>-4.047200000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.470899999999999</v>
+        <v>1.9297</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.635600000000002</v>
+        <v>-5.976799999999999</v>
       </c>
       <c r="V14" t="n">
         <v>26.8416</v>
